--- a/Excel/Vertical/hasil_open_close_total.xlsx
+++ b/Excel/Vertical/hasil_open_close_total.xlsx
@@ -658,13 +658,13 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>28</v>
       </c>
       <c r="E13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -781,10 +781,10 @@
         <v>11</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -981,10 +981,10 @@
         <v>23</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E29">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F29" t="s">
         <v>10</v>
@@ -1018,13 +1018,13 @@
         <v>64</v>
       </c>
       <c r="C31">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D31">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E31">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
         <v>10</v>
